--- a/documents/operations.xlsx
+++ b/documents/operations.xlsx
@@ -516,7 +516,6 @@
           <t>2021-05-14</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>95300</v>
       </c>
@@ -568,7 +567,6 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>101100</v>
       </c>
@@ -620,7 +618,6 @@
           <t>2024-06-26</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>94000</v>
       </c>
@@ -672,7 +669,6 @@
           <t>2022-01-13</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>97300</v>
       </c>
@@ -724,7 +720,6 @@
           <t>2023-02-06</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>83400</v>
       </c>
@@ -776,7 +771,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>101000</v>
       </c>
@@ -828,7 +822,6 @@
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>79400</v>
       </c>
@@ -880,7 +873,6 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>82200</v>
       </c>
@@ -932,7 +924,6 @@
           <t>2019-09-23</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>111600</v>
       </c>
@@ -984,7 +975,6 @@
           <t>2023-06-27</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>120500</v>
       </c>
@@ -1036,7 +1026,6 @@
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>79600</v>
       </c>
@@ -1088,7 +1077,6 @@
           <t>2023-05-13</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>81500</v>
       </c>
@@ -1140,7 +1128,6 @@
           <t>2023-09-20</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>101700</v>
       </c>
@@ -1192,7 +1179,6 @@
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>95500</v>
       </c>
@@ -1244,7 +1230,6 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>79500</v>
       </c>
@@ -1296,7 +1281,6 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>80100</v>
       </c>
@@ -1348,7 +1332,6 @@
           <t>2023-05-08</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
         <v>102000</v>
       </c>
@@ -1400,7 +1383,6 @@
           <t>2019-04-15</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>89100</v>
       </c>
@@ -1452,7 +1434,6 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>76500</v>
       </c>
@@ -1504,7 +1485,6 @@
           <t>2022-04-18</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>87800</v>
       </c>
@@ -1556,7 +1536,6 @@
           <t>2019-09-05</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>90600</v>
       </c>
@@ -1608,7 +1587,6 @@
           <t>2023-03-16</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>109400</v>
       </c>
@@ -1660,7 +1638,6 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
         <v>115700</v>
       </c>
@@ -1712,7 +1689,6 @@
           <t>2024-12-27</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
         <v>103000</v>
       </c>
@@ -1764,7 +1740,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
         <v>78900</v>
       </c>
@@ -1816,7 +1791,6 @@
           <t>2023-01-26</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>88200</v>
       </c>
@@ -1868,7 +1842,6 @@
           <t>2025-07-14</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>72700</v>
       </c>
@@ -1920,7 +1893,6 @@
           <t>2025-07-08</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>66700</v>
       </c>
@@ -1972,7 +1944,6 @@
           <t>2025-05-09</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>114200</v>
       </c>
@@ -2024,7 +1995,6 @@
           <t>2021-01-16</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>81800</v>
       </c>
@@ -2076,7 +2046,6 @@
           <t>2024-03-07</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
         <v>75100</v>
       </c>
@@ -2128,7 +2097,6 @@
           <t>2022-09-11</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>78600</v>
       </c>
@@ -2180,7 +2148,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
         <v>77500</v>
       </c>
@@ -2232,7 +2199,6 @@
           <t>2020-01-16</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
         <v>86900</v>
       </c>
@@ -2284,7 +2250,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
         <v>100400</v>
       </c>
@@ -2336,7 +2301,6 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
         <v>85500</v>
       </c>
@@ -2388,7 +2352,6 @@
           <t>2023-03-22</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
         <v>81600</v>
       </c>
@@ -2440,7 +2403,6 @@
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>84000</v>
       </c>
@@ -2492,7 +2454,6 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
         <v>74700</v>
       </c>
@@ -2544,7 +2505,6 @@
           <t>2023-02-26</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
         <v>93200</v>
       </c>
@@ -2596,7 +2556,6 @@
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
         <v>105000</v>
       </c>
@@ -2648,7 +2607,6 @@
           <t>2021-07-07</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>69000</v>
       </c>
@@ -2700,7 +2658,6 @@
           <t>2021-05-11</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
         <v>84400</v>
       </c>
@@ -2752,7 +2709,6 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
         <v>70400</v>
       </c>
@@ -2804,7 +2760,6 @@
           <t>2018-05-15</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
         <v>94300</v>
       </c>
@@ -2856,7 +2811,6 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
         <v>93800</v>
       </c>
@@ -2908,7 +2862,6 @@
           <t>2022-12-15</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
         <v>118600</v>
       </c>
@@ -2960,7 +2913,6 @@
           <t>2022-10-08</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
         <v>105500</v>
       </c>
@@ -3012,7 +2964,6 @@
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
         <v>76900</v>
       </c>
@@ -3064,7 +3015,6 @@
           <t>2022-05-24</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
         <v>66600</v>
       </c>
@@ -3116,7 +3066,6 @@
           <t>2019-03-24</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
         <v>117100</v>
       </c>
@@ -3168,7 +3117,6 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
         <v>90200</v>
       </c>
@@ -3220,7 +3168,6 @@
           <t>2022-11-28</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
         <v>108900</v>
       </c>
@@ -3272,7 +3219,6 @@
           <t>2019-01-05</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
         <v>88000</v>
       </c>
@@ -3324,7 +3270,6 @@
           <t>2019-12-28</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
         <v>134100</v>
       </c>
@@ -3376,7 +3321,6 @@
           <t>2019-02-27</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
         <v>113200</v>
       </c>
@@ -3428,7 +3372,6 @@
           <t>2024-05-11</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
         <v>97500</v>
       </c>
@@ -3480,7 +3423,6 @@
           <t>2018-01-26</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
         <v>79700</v>
       </c>
@@ -3532,7 +3474,6 @@
           <t>2022-08-05</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
         <v>71100</v>
       </c>
@@ -3584,7 +3525,6 @@
           <t>2023-06-17</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>85100</v>
       </c>
@@ -3636,7 +3576,6 @@
           <t>2019-11-15</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>106100</v>
       </c>
@@ -3688,7 +3627,6 @@
           <t>2024-06-12</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
         <v>69000</v>
       </c>
@@ -3740,7 +3678,6 @@
           <t>2024-04-18</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
         <v>82100</v>
       </c>
@@ -3792,7 +3729,6 @@
           <t>2021-04-24</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
         <v>101800</v>
       </c>
@@ -3844,7 +3780,6 @@
           <t>2019-12-28</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
         <v>103900</v>
       </c>
@@ -3896,7 +3831,6 @@
           <t>2023-05-06</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
         <v>87700</v>
       </c>
@@ -3948,7 +3882,6 @@
           <t>2021-06-21</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
         <v>84100</v>
       </c>
@@ -4000,7 +3933,6 @@
           <t>2019-09-05</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
         <v>75100</v>
       </c>
@@ -4052,7 +3984,6 @@
           <t>2023-09-20</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
         <v>79700</v>
       </c>
@@ -4104,7 +4035,6 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
         <v>96300</v>
       </c>
@@ -4156,7 +4086,6 @@
           <t>2022-06-14</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
         <v>90200</v>
       </c>
@@ -4208,7 +4137,6 @@
           <t>2024-07-11</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
         <v>63300</v>
       </c>
@@ -4260,7 +4188,6 @@
           <t>2018-02-13</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
         <v>91600</v>
       </c>
@@ -4312,7 +4239,6 @@
           <t>2024-06-25</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
         <v>64900</v>
       </c>
@@ -4364,7 +4290,6 @@
           <t>2023-05-15</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
         <v>76800</v>
       </c>
@@ -4416,7 +4341,6 @@
           <t>2019-12-24</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
         <v>132200</v>
       </c>
@@ -4468,7 +4392,6 @@
           <t>2019-12-16</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
         <v>110500</v>
       </c>
@@ -4520,7 +4443,6 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>69200</v>
       </c>
@@ -4572,7 +4494,6 @@
           <t>2023-07-07</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
         <v>92900</v>
       </c>
@@ -4624,7 +4545,6 @@
           <t>2022-12-21</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>91200</v>
       </c>
@@ -4676,7 +4596,6 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>71800</v>
       </c>
@@ -4728,7 +4647,6 @@
           <t>2025-03-03</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
         <v>75700</v>
       </c>
@@ -4780,7 +4698,6 @@
           <t>2021-05-20</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
         <v>84400</v>
       </c>
@@ -4832,7 +4749,6 @@
           <t>2023-11-15</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
         <v>58000</v>
       </c>
@@ -4884,7 +4800,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>85400</v>
       </c>
@@ -4936,7 +4851,6 @@
           <t>2022-02-20</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
         <v>87000</v>
       </c>
@@ -4988,7 +4902,6 @@
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
         <v>63800</v>
       </c>
@@ -5040,7 +4953,6 @@
           <t>2023-02-15</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
         <v>70800</v>
       </c>
@@ -5092,7 +5004,6 @@
           <t>2023-07-12</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
         <v>104900</v>
       </c>
@@ -5144,7 +5055,6 @@
           <t>2022-01-06</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
         <v>83800</v>
       </c>
@@ -5196,7 +5106,6 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
         <v>67100</v>
       </c>
@@ -5248,7 +5157,6 @@
           <t>2019-11-26</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
         <v>84100</v>
       </c>
@@ -5300,7 +5208,6 @@
           <t>2021-06-20</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
         <v>101300</v>
       </c>
@@ -5352,7 +5259,6 @@
           <t>2022-11-12</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
         <v>92500</v>
       </c>
@@ -5404,7 +5310,6 @@
           <t>2023-06-25</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
         <v>92700</v>
       </c>
@@ -5456,7 +5361,6 @@
           <t>2023-04-15</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
         <v>81900</v>
       </c>
@@ -5508,7 +5412,6 @@
           <t>2025-09-03</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
         <v>111300</v>
       </c>
@@ -5560,7 +5463,6 @@
           <t>2019-11-22</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
         <v>93500</v>
       </c>
@@ -5612,7 +5514,6 @@
           <t>2025-12-24</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
         <v>89400</v>
       </c>
@@ -5664,7 +5565,6 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
         <v>72200</v>
       </c>
@@ -5716,7 +5616,6 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
         <v>90300</v>
       </c>
@@ -5768,7 +5667,6 @@
           <t>2022-02-13</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
         <v>92100</v>
       </c>
@@ -5820,7 +5718,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
         <v>74700</v>
       </c>
@@ -5872,7 +5769,6 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
         <v>81700</v>
       </c>
@@ -5924,7 +5820,6 @@
           <t>2023-10-02</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
         <v>104300</v>
       </c>
@@ -5976,7 +5871,6 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
         <v>88900</v>
       </c>
@@ -6028,7 +5922,6 @@
           <t>2019-11-27</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
         <v>88200</v>
       </c>
@@ -6080,7 +5973,6 @@
           <t>2023-08-16</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
         <v>79200</v>
       </c>
@@ -6132,7 +6024,6 @@
           <t>2024-06-14</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
         <v>98400</v>
       </c>
@@ -6184,7 +6075,6 @@
           <t>2024-03-13</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
         <v>101400</v>
       </c>
@@ -6236,7 +6126,6 @@
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
         <v>109400</v>
       </c>
@@ -6288,7 +6177,6 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
         <v>72700</v>
       </c>
@@ -6340,7 +6228,6 @@
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
         <v>77200</v>
       </c>
@@ -6392,7 +6279,6 @@
           <t>2018-12-28</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
         <v>118200</v>
       </c>
@@ -6444,7 +6330,6 @@
           <t>2025-12-25</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="n">
         <v>114500</v>
       </c>
@@ -6496,7 +6381,6 @@
           <t>2024-08-24</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
         <v>120400</v>
       </c>
@@ -6548,7 +6432,6 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
         <v>70500</v>
       </c>
@@ -6600,7 +6483,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
         <v>59900</v>
       </c>
@@ -6942,7 +6824,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -7110,7 +6992,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -7166,7 +7048,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -7278,7 +7160,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -7390,7 +7272,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -7670,7 +7552,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -7838,7 +7720,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -7950,7 +7832,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -7996,7 +7878,6 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
         <v>73600</v>
       </c>
@@ -8058,7 +7939,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -8104,7 +7985,6 @@
           <t>2021-05-03</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
         <v>70600</v>
       </c>
@@ -8558,7 +8438,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -8782,7 +8662,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -8950,7 +8830,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I161" t="n">
@@ -9108,7 +8988,6 @@
           <t>2021-07-22</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
         <v>107500</v>
       </c>
@@ -9450,7 +9329,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -9552,7 +9431,6 @@
           <t>2023-02-28</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
         <v>90200</v>
       </c>
@@ -9670,7 +9548,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I174" t="n">
@@ -9828,7 +9706,6 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
         <v>68000</v>
       </c>
@@ -9890,7 +9767,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -10104,7 +9981,6 @@
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
         <v>109200</v>
       </c>
@@ -10334,7 +10210,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -10390,7 +10266,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I187" t="n">
@@ -10614,7 +10490,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I191" t="n">
@@ -10996,7 +10872,6 @@
           <t>2022-09-04</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
       <c r="G198" t="n">
         <v>77400</v>
       </c>
@@ -11104,7 +10979,6 @@
           <t>2023-05-13</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
       <c r="G200" t="n">
         <v>70500</v>
       </c>
@@ -11502,7 +11376,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I207" t="n">
@@ -11604,7 +11478,6 @@
           <t>2020-08-11</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
         <v>115900</v>
       </c>
@@ -11656,7 +11529,6 @@
           <t>2024-07-20</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
         <v>93400</v>
       </c>
@@ -11718,7 +11590,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I211" t="n">
@@ -11830,7 +11702,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I213" t="n">
@@ -11942,7 +11814,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I215" t="n">
@@ -12502,7 +12374,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I225" t="n">
@@ -12558,7 +12430,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I226" t="n">
@@ -12726,7 +12598,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I229" t="n">
@@ -12838,7 +12710,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I231" t="n">
@@ -13006,7 +12878,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I234" t="n">
@@ -13454,7 +13326,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I242" t="n">
@@ -13622,7 +13494,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I245" t="n">
@@ -13734,7 +13606,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I247" t="n">
@@ -13790,7 +13662,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I248" t="n">

--- a/documents/operations.xlsx
+++ b/documents/operations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L249"/>
+  <dimension ref="A1:L254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,12 +720,17 @@
           <t>2023-02-06</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="G6" t="n">
         <v>83400</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1026,12 +1031,17 @@
           <t>2021-09-14</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="G12" t="n">
         <v>79600</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1485,12 +1495,17 @@
           <t>2022-04-18</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
       <c r="G21" t="n">
         <v>87800</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1689,12 +1704,17 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
       <c r="G25" t="n">
         <v>103000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1791,12 +1811,17 @@
           <t>2023-01-26</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="G27" t="n">
         <v>88200</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1893,12 +1918,17 @@
           <t>2025-07-08</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="G29" t="n">
         <v>66700</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2046,12 +2076,17 @@
           <t>2024-03-07</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="G32" t="n">
         <v>75100</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2199,12 +2234,17 @@
           <t>2020-01-16</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="G35" t="n">
         <v>86900</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2352,12 +2392,17 @@
           <t>2023-03-22</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="G38" t="n">
         <v>81600</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2403,12 +2448,17 @@
           <t>2024-06-16</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="G39" t="n">
         <v>84000</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2556,12 +2606,17 @@
           <t>2022-09-26</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
       <c r="G42" t="n">
         <v>105000</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2607,12 +2662,17 @@
           <t>2021-07-07</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="G43" t="n">
         <v>69000</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2913,12 +2973,17 @@
           <t>2022-10-08</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
       <c r="G49" t="n">
         <v>105500</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3168,12 +3233,17 @@
           <t>2022-11-28</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
       <c r="G54" t="n">
         <v>108900</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3780,12 +3850,17 @@
           <t>2019-12-28</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
       <c r="G66" t="n">
         <v>103900</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4137,12 +4212,17 @@
           <t>2024-07-11</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
       <c r="G73" t="n">
         <v>63300</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4698,12 +4778,17 @@
           <t>2021-05-20</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="G84" t="n">
         <v>84400</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -4800,12 +4885,17 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
       <c r="G86" t="n">
         <v>85400</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -5004,12 +5094,17 @@
           <t>2023-07-12</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="G90" t="n">
         <v>104900</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -5106,12 +5201,17 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
       <c r="G92" t="n">
         <v>67100</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -5157,12 +5257,17 @@
           <t>2019-11-26</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
       <c r="G93" t="n">
         <v>84100</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -5514,12 +5619,17 @@
           <t>2025-12-24</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="G100" t="n">
         <v>89400</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -5922,12 +6032,17 @@
           <t>2019-11-27</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="G108" t="n">
         <v>88200</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -6177,12 +6292,17 @@
           <t>2022-11-01</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
       <c r="G113" t="n">
         <v>72700</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -6279,12 +6399,17 @@
           <t>2018-12-28</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="G115" t="n">
         <v>118200</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -6483,12 +6608,17 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
       <c r="G119" t="n">
         <v>59900</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -13735,6 +13865,261 @@
       <c r="L249" t="inlineStr">
         <is>
           <t>Hispanic</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Rose Howard</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1995-03-31</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Systems Administrator</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>81700</v>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>3</v>
+      </c>
+      <c r="J250" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Phillip Adams</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>1980-11-02</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Operations Coordinator</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>79000</v>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I251" t="n">
+        <v>1</v>
+      </c>
+      <c r="J251" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Patricia Wallace</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1969-11-27</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>97000</v>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Marie Jones</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>1990-05-23</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Systems Administrator</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>82900</v>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I253" t="n">
+        <v>3</v>
+      </c>
+      <c r="J253" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Carol Mitchell</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>1995-01-21</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>110100</v>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I254" t="n">
+        <v>2</v>
+      </c>
+      <c r="J254" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>White</t>
         </is>
       </c>
     </row>
